--- a/docs/Check.xlsx
+++ b/docs/Check.xlsx
@@ -1069,7 +1069,7 @@
         <v>21</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>54</v>

--- a/docs/Check.xlsx
+++ b/docs/Check.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="pfBXH7u2jDk2e6Z4O6VZK6LYRM2un/7UTiDZUlbbH/Q="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="14VRWddkwE3nQBNe3yG7PuIU7POwI5/YURLjb8KCDvM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="68">
   <si>
     <t>Группа проверок/модуль</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Формат даты (день, месяц, год) и сама дата не соответствует той, что указывалась при создании</t>
+  </si>
+  <si>
+    <t>Редактирование уже созданной новости</t>
   </si>
   <si>
     <t>После создания новости дата публикации в списке соответствует выбранной при создании</t>
@@ -945,12 +948,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="12" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>8</v>
@@ -958,27 +961,27 @@
       <c r="E24" s="10"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="C25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11"/>
       <c r="B26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>13</v>
+      <c r="C26" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>8</v>
@@ -986,52 +989,50 @@
       <c r="E26" s="10"/>
     </row>
     <row r="27">
-      <c r="A27" s="14"/>
+      <c r="A27" s="11"/>
       <c r="B27" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14"/>
+      <c r="B28" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="12" t="s">
+      <c r="D28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="B29" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11"/>
-      <c r="B29" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>13</v>
-      </c>
       <c r="D29" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>48</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E29" s="10"/>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
-      <c r="B30" s="19" t="s">
-        <v>49</v>
+      <c r="B30" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>13</v>
@@ -1040,11 +1041,11 @@
         <v>10</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="19" t="s">
         <v>50</v>
       </c>
@@ -1055,38 +1056,40 @@
         <v>10</v>
       </c>
       <c r="E31" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14"/>
+      <c r="B32" s="19" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="C32" s="9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="19" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12" t="s">
+      <c r="C33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="10"/>
     </row>
     <row r="34">
       <c r="A34" s="11"/>
@@ -1159,7 +1162,7 @@
         <v>61</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>8</v>
@@ -1167,12 +1170,12 @@
       <c r="E39" s="10"/>
     </row>
     <row r="40">
-      <c r="A40" s="14"/>
+      <c r="A40" s="11"/>
       <c r="B40" s="12" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>8</v>
@@ -1180,50 +1183,63 @@
       <c r="E40" s="10"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="14"/>
+      <c r="B41" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="C41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="9" t="s">
+      <c r="B42" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14"/>
-      <c r="B42" s="19" t="s">
+      <c r="E42" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="10"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14"/>
+      <c r="B43" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A40"/>
-    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A11:A25"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C42">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C43">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D42">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D43">
       <formula1>"Пройден,Не пройден,N/A"</formula1>
     </dataValidation>
   </dataValidations>
